--- a/SCHOOL_RESULT_SYSTEM/CLASS_DATA/THREE.xlsx
+++ b/SCHOOL_RESULT_SYSTEM/CLASS_DATA/THREE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SYTEM\SCHOOL_RESULT_SYSTEM\CLASS_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F22765-BC24-4BC6-9BEA-ADA015B7AD62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9CFD4E7-2B2D-443A-9389-26C32FDA6032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{CED4DE98-B28C-4730-9DA8-A368C1B97B73}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>RollNo</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>Islamiat_Max</t>
+  </si>
+  <si>
+    <t>Ali</t>
   </si>
 </sst>
 </file>
@@ -587,17 +590,35 @@
       <c r="A3" s="3">
         <v>2</v>
       </c>
+      <c r="B3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3">
+        <v>40</v>
+      </c>
       <c r="D3" s="3">
         <v>50</v>
       </c>
+      <c r="E3" s="3">
+        <v>50</v>
+      </c>
       <c r="F3" s="3">
         <v>50</v>
       </c>
+      <c r="G3" s="3">
+        <v>50</v>
+      </c>
       <c r="H3" s="3">
         <v>50</v>
       </c>
+      <c r="I3" s="3">
+        <v>24</v>
+      </c>
       <c r="J3" s="3">
         <v>25</v>
+      </c>
+      <c r="K3" s="3">
+        <v>49</v>
       </c>
       <c r="L3" s="3">
         <v>50</v>

--- a/SCHOOL_RESULT_SYSTEM/CLASS_DATA/THREE.xlsx
+++ b/SCHOOL_RESULT_SYSTEM/CLASS_DATA/THREE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SYTEM\SCHOOL_RESULT_SYSTEM\CLASS_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9CFD4E7-2B2D-443A-9389-26C32FDA6032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45FB34D0-3EB4-4CDA-BB5F-A2746EA634D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{CED4DE98-B28C-4730-9DA8-A368C1B97B73}"/>
   </bookViews>

--- a/SCHOOL_RESULT_SYSTEM/CLASS_DATA/THREE.xlsx
+++ b/SCHOOL_RESULT_SYSTEM/CLASS_DATA/THREE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SYTEM\SCHOOL_RESULT_SYSTEM\CLASS_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45FB34D0-3EB4-4CDA-BB5F-A2746EA634D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36ABD76-7108-4D4E-A508-9B5BEB339ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{CED4DE98-B28C-4730-9DA8-A368C1B97B73}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>RollNo</t>
   </si>
@@ -78,6 +78,12 @@
   </si>
   <si>
     <t>Ali</t>
+  </si>
+  <si>
+    <t>Chem</t>
+  </si>
+  <si>
+    <t>Chem_Max</t>
   </si>
 </sst>
 </file>
@@ -499,10 +505,12 @@
     <col min="7" max="7" width="15.85546875" style="3" customWidth="1"/>
     <col min="8" max="8" width="16.42578125" style="3" customWidth="1"/>
     <col min="9" max="9" width="13.5703125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="18" style="3" customWidth="1"/>
+    <col min="10" max="10" width="17.85546875" style="3" customWidth="1"/>
     <col min="11" max="11" width="14.140625" style="3" customWidth="1"/>
     <col min="12" max="12" width="17.42578125" style="3" customWidth="1"/>
-    <col min="13" max="16" width="12.140625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="14.140625" style="3" customWidth="1"/>
+    <col min="14" max="14" width="17.42578125" style="3" customWidth="1"/>
+    <col min="15" max="16" width="12.140625" style="3" customWidth="1"/>
     <col min="17" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
@@ -543,8 +551,12 @@
       <c r="L1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
+      <c r="M1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
@@ -585,6 +597,12 @@
       <c r="L2" s="3">
         <v>50</v>
       </c>
+      <c r="M2" s="3">
+        <v>19</v>
+      </c>
+      <c r="N2" s="3">
+        <v>50</v>
+      </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
@@ -623,6 +641,12 @@
       <c r="L3" s="3">
         <v>50</v>
       </c>
+      <c r="M3" s="3">
+        <v>49</v>
+      </c>
+      <c r="N3" s="3">
+        <v>50</v>
+      </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
@@ -643,6 +667,9 @@
       <c r="L4" s="3">
         <v>50</v>
       </c>
+      <c r="N4" s="3">
+        <v>50</v>
+      </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
@@ -663,6 +690,9 @@
       <c r="L5" s="3">
         <v>50</v>
       </c>
+      <c r="N5" s="3">
+        <v>50</v>
+      </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
@@ -683,6 +713,9 @@
       <c r="L6" s="3">
         <v>50</v>
       </c>
+      <c r="N6" s="3">
+        <v>50</v>
+      </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
@@ -703,6 +736,9 @@
       <c r="L7" s="3">
         <v>50</v>
       </c>
+      <c r="N7" s="3">
+        <v>50</v>
+      </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
@@ -723,6 +759,9 @@
       <c r="L8" s="3">
         <v>50</v>
       </c>
+      <c r="N8" s="3">
+        <v>50</v>
+      </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
@@ -743,6 +782,9 @@
       <c r="L9" s="3">
         <v>50</v>
       </c>
+      <c r="N9" s="3">
+        <v>50</v>
+      </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
@@ -763,6 +805,9 @@
       <c r="L10" s="3">
         <v>50</v>
       </c>
+      <c r="N10" s="3">
+        <v>50</v>
+      </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
@@ -783,6 +828,9 @@
       <c r="L11" s="3">
         <v>50</v>
       </c>
+      <c r="N11" s="3">
+        <v>50</v>
+      </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
@@ -803,6 +851,9 @@
       <c r="L12" s="3">
         <v>50</v>
       </c>
+      <c r="N12" s="3">
+        <v>50</v>
+      </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
@@ -823,6 +874,9 @@
       <c r="L13" s="3">
         <v>50</v>
       </c>
+      <c r="N13" s="3">
+        <v>50</v>
+      </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
@@ -843,6 +897,9 @@
       <c r="L14" s="3">
         <v>50</v>
       </c>
+      <c r="N14" s="3">
+        <v>50</v>
+      </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
@@ -863,6 +920,9 @@
       <c r="L15" s="3">
         <v>50</v>
       </c>
+      <c r="N15" s="3">
+        <v>50</v>
+      </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
@@ -883,8 +943,11 @@
       <c r="L16" s="3">
         <v>50</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N16" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -903,8 +966,11 @@
       <c r="L17" s="3">
         <v>50</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N17" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -921,6 +987,9 @@
         <v>25</v>
       </c>
       <c r="L18" s="3">
+        <v>50</v>
+      </c>
+      <c r="N18" s="3">
         <v>50</v>
       </c>
     </row>

--- a/SCHOOL_RESULT_SYSTEM/CLASS_DATA/THREE.xlsx
+++ b/SCHOOL_RESULT_SYSTEM/CLASS_DATA/THREE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SYTEM\SCHOOL_RESULT_SYSTEM\CLASS_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36ABD76-7108-4D4E-A508-9B5BEB339ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED7FE0A-DFC9-475F-B470-39ED25F3E44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{CED4DE98-B28C-4730-9DA8-A368C1B97B73}"/>
+    <workbookView xWindow="3045" yWindow="4215" windowWidth="21600" windowHeight="11385" xr2:uid="{CED4DE98-B28C-4730-9DA8-A368C1B97B73}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>RollNo</t>
   </si>
@@ -78,12 +78,6 @@
   </si>
   <si>
     <t>Ali</t>
-  </si>
-  <si>
-    <t>Chem</t>
-  </si>
-  <si>
-    <t>Chem_Max</t>
   </si>
 </sst>
 </file>
@@ -551,12 +545,8 @@
       <c r="L1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
@@ -597,12 +587,6 @@
       <c r="L2" s="3">
         <v>50</v>
       </c>
-      <c r="M2" s="3">
-        <v>19</v>
-      </c>
-      <c r="N2" s="3">
-        <v>50</v>
-      </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
@@ -641,12 +625,6 @@
       <c r="L3" s="3">
         <v>50</v>
       </c>
-      <c r="M3" s="3">
-        <v>49</v>
-      </c>
-      <c r="N3" s="3">
-        <v>50</v>
-      </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
@@ -667,9 +645,6 @@
       <c r="L4" s="3">
         <v>50</v>
       </c>
-      <c r="N4" s="3">
-        <v>50</v>
-      </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
@@ -690,9 +665,6 @@
       <c r="L5" s="3">
         <v>50</v>
       </c>
-      <c r="N5" s="3">
-        <v>50</v>
-      </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
@@ -713,9 +685,6 @@
       <c r="L6" s="3">
         <v>50</v>
       </c>
-      <c r="N6" s="3">
-        <v>50</v>
-      </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
@@ -736,9 +705,6 @@
       <c r="L7" s="3">
         <v>50</v>
       </c>
-      <c r="N7" s="3">
-        <v>50</v>
-      </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
@@ -759,9 +725,6 @@
       <c r="L8" s="3">
         <v>50</v>
       </c>
-      <c r="N8" s="3">
-        <v>50</v>
-      </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
@@ -782,9 +745,6 @@
       <c r="L9" s="3">
         <v>50</v>
       </c>
-      <c r="N9" s="3">
-        <v>50</v>
-      </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
@@ -805,9 +765,6 @@
       <c r="L10" s="3">
         <v>50</v>
       </c>
-      <c r="N10" s="3">
-        <v>50</v>
-      </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
@@ -828,9 +785,6 @@
       <c r="L11" s="3">
         <v>50</v>
       </c>
-      <c r="N11" s="3">
-        <v>50</v>
-      </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
@@ -851,9 +805,6 @@
       <c r="L12" s="3">
         <v>50</v>
       </c>
-      <c r="N12" s="3">
-        <v>50</v>
-      </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
@@ -874,9 +825,6 @@
       <c r="L13" s="3">
         <v>50</v>
       </c>
-      <c r="N13" s="3">
-        <v>50</v>
-      </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
@@ -897,9 +845,6 @@
       <c r="L14" s="3">
         <v>50</v>
       </c>
-      <c r="N14" s="3">
-        <v>50</v>
-      </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
@@ -920,9 +865,6 @@
       <c r="L15" s="3">
         <v>50</v>
       </c>
-      <c r="N15" s="3">
-        <v>50</v>
-      </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
@@ -943,11 +885,8 @@
       <c r="L16" s="3">
         <v>50</v>
       </c>
-      <c r="N16" s="3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -966,11 +905,8 @@
       <c r="L17" s="3">
         <v>50</v>
       </c>
-      <c r="N17" s="3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -987,9 +923,6 @@
         <v>25</v>
       </c>
       <c r="L18" s="3">
-        <v>50</v>
-      </c>
-      <c r="N18" s="3">
         <v>50</v>
       </c>
     </row>

--- a/SCHOOL_RESULT_SYSTEM/CLASS_DATA/THREE.xlsx
+++ b/SCHOOL_RESULT_SYSTEM/CLASS_DATA/THREE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SYTEM\SCHOOL_RESULT_SYSTEM\CLASS_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED7FE0A-DFC9-475F-B470-39ED25F3E44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C941E9E-A127-44E3-8C15-637AC4F3369E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3045" yWindow="4215" windowWidth="21600" windowHeight="11385" xr2:uid="{CED4DE98-B28C-4730-9DA8-A368C1B97B73}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{CED4DE98-B28C-4730-9DA8-A368C1B97B73}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>RollNo</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>Ali</t>
+  </si>
+  <si>
+    <t>waleed</t>
   </si>
 </sst>
 </file>
@@ -630,17 +633,35 @@
       <c r="A4" s="3">
         <v>3</v>
       </c>
+      <c r="B4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="3">
+        <v>49</v>
+      </c>
       <c r="D4" s="3">
         <v>50</v>
       </c>
+      <c r="E4" s="3">
+        <v>24</v>
+      </c>
       <c r="F4" s="3">
         <v>50</v>
       </c>
+      <c r="G4" s="3">
+        <v>50</v>
+      </c>
       <c r="H4" s="3">
         <v>50</v>
       </c>
+      <c r="I4" s="3">
+        <v>23</v>
+      </c>
       <c r="J4" s="3">
         <v>25</v>
+      </c>
+      <c r="K4" s="3">
+        <v>48</v>
       </c>
       <c r="L4" s="3">
         <v>50</v>
